--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7AA1E34-DB22-49EE-9FA7-15982803E52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFDACEA-EB3B-4D14-AC67-8263F0026758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="44">
   <si>
     <t>Jugador</t>
   </si>
@@ -137,6 +137,21 @@
   </si>
   <si>
     <t xml:space="preserve">Marcello_Rodriguez </t>
+  </si>
+  <si>
+    <t>Lateralidad</t>
+  </si>
+  <si>
+    <t>Izquierdo</t>
+  </si>
+  <si>
+    <t>Derecho</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Zurdo</t>
   </si>
 </sst>
 </file>
@@ -681,11 +696,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:B31" totalsRowShown="0">
-  <autoFilter ref="A1:B31" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:C31" totalsRowShown="0">
+  <autoFilter ref="A1:C31" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+  <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
+    <tableColumn id="3" xr3:uid="{AFFF0E67-2FE5-4EA2-B42B-E730FFF02CEB}" name="Lateralidad"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -988,255 +1004,353 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
       <c r="B25" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>38</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFDACEA-EB3B-4D14-AC67-8263F0026758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6948DFCD-A4B4-4D61-9D68-B3A980A8E3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
+    <workbookView xWindow="4080" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="48">
   <si>
     <t>Jugador</t>
   </si>
@@ -152,6 +152,18 @@
   </si>
   <si>
     <t>Zurdo</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>hasta vuelta sustacha</t>
   </si>
 </sst>
 </file>
@@ -696,12 +708,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:C31" totalsRowShown="0">
-  <autoFilter ref="A1:C31" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:D31" totalsRowShown="0">
+  <autoFilter ref="A1:D31" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
     <tableColumn id="3" xr3:uid="{AFFF0E67-2FE5-4EA2-B42B-E730FFF02CEB}" name="Lateralidad"/>
+    <tableColumn id="4" xr3:uid="{E7F89486-0E13-44F6-BA58-D66FF74E187A}" name="GPS"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1004,15 +1017,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="C1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1033,8 +1050,11 @@
       <c r="C2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1044,8 +1064,11 @@
       <c r="C3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1055,8 +1078,11 @@
       <c r="C4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1066,8 +1092,11 @@
       <c r="C5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1077,8 +1106,11 @@
       <c r="C6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1088,8 +1120,11 @@
       <c r="C7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1099,8 +1134,11 @@
       <c r="C8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1110,8 +1148,11 @@
       <c r="C9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1121,8 +1162,11 @@
       <c r="C10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1132,8 +1176,11 @@
       <c r="C11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1143,8 +1190,11 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1154,8 +1204,11 @@
       <c r="C13" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1165,8 +1218,11 @@
       <c r="C14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1176,8 +1232,11 @@
       <c r="C15" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1187,8 +1246,11 @@
       <c r="C16" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1198,8 +1260,11 @@
       <c r="C17" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1209,8 +1274,11 @@
       <c r="C18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1220,8 +1288,11 @@
       <c r="C19" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1231,8 +1302,11 @@
       <c r="C20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1242,8 +1316,11 @@
       <c r="C21" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1253,8 +1330,11 @@
       <c r="C22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1264,8 +1344,11 @@
       <c r="C23" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1275,8 +1358,11 @@
       <c r="C24" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1286,8 +1372,11 @@
       <c r="C25" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1297,8 +1386,11 @@
       <c r="C26" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1308,8 +1400,11 @@
       <c r="C27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1319,8 +1414,11 @@
       <c r="C28" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1330,8 +1428,11 @@
       <c r="C29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1341,8 +1442,11 @@
       <c r="C30" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1351,6 +1455,9 @@
       </c>
       <c r="C31" t="s">
         <v>42</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6948DFCD-A4B4-4D61-9D68-B3A980A8E3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAD35BC-AD02-4E4B-8519-96AFC8F921F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="49">
   <si>
     <t>Jugador</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>hasta vuelta sustacha</t>
+  </si>
+  <si>
+    <t>Alex_Palacios</t>
   </si>
 </sst>
 </file>
@@ -708,8 +711,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:D31" totalsRowShown="0">
-  <autoFilter ref="A1:D31" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:D32" totalsRowShown="0">
+  <autoFilter ref="A1:D32" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
@@ -1017,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1460,6 +1463,20 @@
         <v>46</v>
       </c>
     </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAD35BC-AD02-4E4B-8519-96AFC8F921F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D16E69-A1D0-43FC-80DA-A506BB53B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="77">
   <si>
     <t>Jugador</t>
   </si>
@@ -121,9 +121,6 @@
     <t xml:space="preserve">Presley_Osarenkhoe </t>
   </si>
   <si>
-    <t xml:space="preserve">Luca _Valentino_Scaffetti </t>
-  </si>
-  <si>
     <t>Jaime_Munoz_Garcia</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
   </si>
   <si>
-    <t xml:space="preserve">Marcello_Rodriguez </t>
-  </si>
-  <si>
     <t>Lateralidad</t>
   </si>
   <si>
@@ -167,13 +161,103 @@
   </si>
   <si>
     <t>Alex_Palacios</t>
+  </si>
+  <si>
+    <t>fotos</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=1</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=2</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=3</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=4</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=5</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=6</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=7</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=8</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=9</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=10</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=11</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=12</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=13</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=14</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=15</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=16</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=17</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=18</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=19</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=20</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=21</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=22</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=23</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=24</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=25</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=26</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=27</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=28</t>
+  </si>
+  <si>
+    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +388,20 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -606,7 +704,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -649,11 +747,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -685,6 +785,7 @@
     <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Hipervínculo" xfId="42" builtinId="8"/>
     <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,13 +812,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:D32" totalsRowShown="0">
-  <autoFilter ref="A1:D32" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:E30" totalsRowShown="0">
+  <autoFilter ref="A1:E30" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
     <tableColumn id="3" xr3:uid="{AFFF0E67-2FE5-4EA2-B42B-E730FFF02CEB}" name="Lateralidad"/>
     <tableColumn id="4" xr3:uid="{E7F89486-0E13-44F6-BA58-D66FF74E187A}" name="GPS"/>
+    <tableColumn id="5" xr3:uid="{038AA75F-12A6-422C-9DEE-93BD0F8D3D9F}" name="fotos"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1020,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1029,7 +1131,7 @@
     <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1037,13 +1139,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1051,13 +1156,16 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1065,13 +1173,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1079,13 +1190,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1093,13 +1207,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1107,13 +1224,16 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1121,13 +1241,16 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1135,13 +1258,16 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1149,13 +1275,16 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1163,13 +1292,16 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1177,13 +1309,16 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1191,13 +1326,16 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1205,13 +1343,16 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1219,13 +1360,16 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1233,13 +1377,16 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1247,13 +1394,16 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1261,13 +1411,16 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1275,13 +1428,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1289,13 +1445,16 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1303,13 +1462,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1317,13 +1479,16 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1331,13 +1496,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1345,13 +1513,16 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1359,13 +1530,16 @@
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1373,114 +1547,109 @@
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
         <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
       <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s">
         <v>12</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" t="s">
-        <v>3</v>
       </c>
       <c r="C30" t="s">
         <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{E58D5341-CB5C-4A79-978F-0588DCAE0E3F}"/>
+    <hyperlink ref="E3:E30" r:id="rId2" display="https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=1" xr:uid="{03678E26-8C6B-4144-A5CA-5C2988DDDDBF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D16E69-A1D0-43FC-80DA-A506BB53B51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E43700-830D-4CE5-8452-FA900E871BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="49">
   <si>
     <t>Jugador</t>
   </si>
@@ -166,91 +166,7 @@
     <t>fotos</t>
   </si>
   <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=1</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=2</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=3</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=4</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=5</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=6</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=7</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=8</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=9</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=10</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=11</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=12</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=13</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=14</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=15</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=16</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=17</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=18</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=19</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=20</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=21</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=22</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=23</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=24</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=25</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=26</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=27</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=28</t>
-  </si>
-  <si>
-    <t>https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=29</t>
+    <t>https://www.clipartmax.com/png/middle/265-2659558_cristiano-ronaldo-clipart-ronaldo-png-cristiano-ronaldo-portugal-png.png</t>
   </si>
 </sst>
 </file>
@@ -1179,7 +1095,7 @@
         <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1196,7 +1112,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1213,7 +1129,7 @@
         <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1230,7 +1146,7 @@
         <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1247,7 +1163,7 @@
         <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1264,7 +1180,7 @@
         <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1281,7 +1197,7 @@
         <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1298,7 +1214,7 @@
         <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1315,7 +1231,7 @@
         <v>43</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1332,7 +1248,7 @@
         <v>44</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1349,7 +1265,7 @@
         <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1366,7 +1282,7 @@
         <v>43</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1383,7 +1299,7 @@
         <v>43</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1400,7 +1316,7 @@
         <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1417,7 +1333,7 @@
         <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1434,7 +1350,7 @@
         <v>44</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1451,7 +1367,7 @@
         <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1468,7 +1384,7 @@
         <v>43</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1485,7 +1401,7 @@
         <v>44</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1502,7 +1418,7 @@
         <v>43</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1519,7 +1435,7 @@
         <v>43</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1536,7 +1452,7 @@
         <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1553,7 +1469,7 @@
         <v>44</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1570,7 +1486,7 @@
         <v>44</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1587,7 +1503,7 @@
         <v>43</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1604,7 +1520,7 @@
         <v>44</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1621,7 +1537,7 @@
         <v>43</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1638,18 +1554,14 @@
         <v>43</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{E58D5341-CB5C-4A79-978F-0588DCAE0E3F}"/>
-    <hyperlink ref="E3:E30" r:id="rId2" display="https://cdn.resfu.com/img_data/players/medium/28185.jpg?size=120x&amp;lossy=1" xr:uid="{03678E26-8C6B-4144-A5CA-5C2988DDDDBF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E43700-830D-4CE5-8452-FA900E871BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5666A6-304B-4B12-B2B6-7D3D4E96A5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
     <t>fotos</t>
   </si>
   <si>
-    <t>https://www.clipartmax.com/png/middle/265-2659558_cristiano-ronaldo-clipart-ronaldo-png-cristiano-ronaldo-portugal-png.png</t>
+    <t>https://banner2.cleanpng.com/cb2/wms/piv/v21en33wa.webp</t>
   </si>
 </sst>
 </file>

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5666A6-304B-4B12-B2B6-7D3D4E96A5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E26302-68FC-4C63-BC02-59CABB38C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="52">
   <si>
     <t>Jugador</t>
   </si>
@@ -167,13 +167,22 @@
   </si>
   <si>
     <t>https://banner2.cleanpng.com/cb2/wms/piv/v21en33wa.webp</t>
+  </si>
+  <si>
+    <t>Diestro</t>
+  </si>
+  <si>
+    <t>Nacimiento</t>
+  </si>
+  <si>
+    <t>Pierna hábil</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,8 +331,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,8 +517,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -619,6 +639,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9EAD3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9EAD3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9EAD3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9EAD3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9EAD3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9EAD3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -665,9 +741,33 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="14" fontId="20" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -714,7 +814,89 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFD9EAD3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFD9EAD3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF434343"/>
+        <name val="Roboto"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD9EAD3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFD9EAD3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFD9EAD3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -728,14 +910,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:E30" totalsRowShown="0">
-  <autoFilter ref="A1:E30" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G30" totalsRowShown="0">
+  <autoFilter ref="A1:G30" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
     <tableColumn id="3" xr3:uid="{AFFF0E67-2FE5-4EA2-B42B-E730FFF02CEB}" name="Lateralidad"/>
     <tableColumn id="4" xr3:uid="{E7F89486-0E13-44F6-BA58-D66FF74E187A}" name="GPS"/>
     <tableColumn id="5" xr3:uid="{038AA75F-12A6-422C-9DEE-93BD0F8D3D9F}" name="fotos"/>
+    <tableColumn id="7" xr3:uid="{609CB956-671E-4A9A-8D90-58B47CE01434}" name="Nacimiento" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{593A8239-F4DD-4DA3-B9D8-7949AFA261E8}" name="Pierna hábil" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1038,16 +1222,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1063,8 +1248,14 @@
       <c r="E1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1080,8 +1271,14 @@
       <c r="E2" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="2">
+        <v>39786</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1097,8 +1294,14 @@
       <c r="E3" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="4">
+        <v>39461</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1114,8 +1317,14 @@
       <c r="E4" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="4">
+        <v>39544</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1131,8 +1340,14 @@
       <c r="E5" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="4">
+        <v>39672</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1148,8 +1363,14 @@
       <c r="E6" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="4">
+        <v>39519</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1165,8 +1386,14 @@
       <c r="E7" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="4">
+        <v>39512</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1182,8 +1409,14 @@
       <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="4">
+        <v>39512</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1199,8 +1432,14 @@
       <c r="E9" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="4">
+        <v>39507</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1216,8 +1455,14 @@
       <c r="E10" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="4">
+        <v>39866</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1233,8 +1478,14 @@
       <c r="E11" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="4">
+        <v>39755</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1250,8 +1501,14 @@
       <c r="E12" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="4">
+        <v>39492</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1267,8 +1524,14 @@
       <c r="E13" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="4">
+        <v>39724</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1284,8 +1547,14 @@
       <c r="E14" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="4">
+        <v>39826</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1301,8 +1570,14 @@
       <c r="E15" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="4">
+        <v>39660</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1318,8 +1593,14 @@
       <c r="E16" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="4">
+        <v>39463</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1335,8 +1616,14 @@
       <c r="E17" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="4">
+        <v>39507</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1352,8 +1639,14 @@
       <c r="E18" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="4">
+        <v>39547</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1369,8 +1662,14 @@
       <c r="E19" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="4">
+        <v>39644</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1386,8 +1685,14 @@
       <c r="E20" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="4">
+        <v>39992</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1403,8 +1708,14 @@
       <c r="E21" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="4">
+        <v>39557</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1420,8 +1731,14 @@
       <c r="E22" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="4">
+        <v>39582</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1437,8 +1754,14 @@
       <c r="E23" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="4">
+        <v>39682</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1454,8 +1777,14 @@
       <c r="E24" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="4">
+        <v>39468</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1471,8 +1800,14 @@
       <c r="E25" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="4">
+        <v>39783</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1488,8 +1823,14 @@
       <c r="E26" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" s="4">
+        <v>39458</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1505,8 +1846,14 @@
       <c r="E27" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" s="4">
+        <v>39753</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1522,8 +1869,14 @@
       <c r="E28" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" s="4">
+        <v>39505</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1539,8 +1892,14 @@
       <c r="E29" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" s="6">
+        <v>39753</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -1556,6 +1915,8 @@
       <c r="E30" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E26302-68FC-4C63-BC02-59CABB38C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -1230,6 +1230,8 @@
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC73D70E-9FAD-44D2-BF04-B192888E39D9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="49">
   <si>
     <t>Jugador</t>
   </si>
@@ -148,18 +148,6 @@
     <t>Zurdo</t>
   </si>
   <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>hasta vuelta sustacha</t>
-  </si>
-  <si>
     <t>Alex_Palacios</t>
   </si>
   <si>
@@ -176,6 +164,9 @@
   </si>
   <si>
     <t>Pierna hábil</t>
+  </si>
+  <si>
+    <t>PASSWORD</t>
   </si>
 </sst>
 </file>
@@ -916,7 +907,7 @@
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
     <tableColumn id="3" xr3:uid="{AFFF0E67-2FE5-4EA2-B42B-E730FFF02CEB}" name="Lateralidad"/>
-    <tableColumn id="4" xr3:uid="{E7F89486-0E13-44F6-BA58-D66FF74E187A}" name="GPS"/>
+    <tableColumn id="4" xr3:uid="{E7F89486-0E13-44F6-BA58-D66FF74E187A}" name="PASSWORD"/>
     <tableColumn id="5" xr3:uid="{038AA75F-12A6-422C-9DEE-93BD0F8D3D9F}" name="fotos"/>
     <tableColumn id="7" xr3:uid="{609CB956-671E-4A9A-8D90-58B47CE01434}" name="Nacimiento" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{593A8239-F4DD-4DA3-B9D8-7949AFA261E8}" name="Pierna hábil" dataDxfId="0"/>
@@ -1245,16 +1236,16 @@
         <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
         <v>47</v>
-      </c>
-      <c r="F1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1267,11 +1258,11 @@
       <c r="C2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
-        <v>43</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F2" s="2">
         <v>39786</v>
@@ -1290,17 +1281,17 @@
       <c r="C3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
-        <v>44</v>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F3" s="4">
         <v>39461</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1313,17 +1304,17 @@
       <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
-        <v>43</v>
+      <c r="D4">
+        <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F4" s="4">
         <v>39544</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1336,17 +1327,17 @@
       <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
-        <v>43</v>
+      <c r="D5">
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F5" s="4">
         <v>39672</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1359,11 +1350,11 @@
       <c r="C6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
-        <v>43</v>
+      <c r="D6">
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F6" s="4">
         <v>39519</v>
@@ -1382,17 +1373,17 @@
       <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
-        <v>43</v>
+      <c r="D7">
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F7" s="4">
         <v>39512</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1405,17 +1396,17 @@
       <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" t="s">
-        <v>45</v>
+      <c r="D8">
+        <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F8" s="4">
         <v>39512</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1428,11 +1419,11 @@
       <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" t="s">
-        <v>43</v>
+      <c r="D9">
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F9" s="4">
         <v>39507</v>
@@ -1451,11 +1442,11 @@
       <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" t="s">
-        <v>44</v>
+      <c r="D10">
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4">
         <v>39866</v>
@@ -1474,17 +1465,17 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" t="s">
-        <v>43</v>
+      <c r="D11">
+        <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F11" s="4">
         <v>39755</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1497,17 +1488,17 @@
       <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
-        <v>44</v>
+      <c r="D12">
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F12" s="4">
         <v>39492</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1520,11 +1511,11 @@
       <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="D13" t="s">
-        <v>43</v>
+      <c r="D13">
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F13" s="4">
         <v>39724</v>
@@ -1543,17 +1534,17 @@
       <c r="C14" t="s">
         <v>39</v>
       </c>
-      <c r="D14" t="s">
-        <v>43</v>
+      <c r="D14">
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F14" s="4">
         <v>39826</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1566,17 +1557,17 @@
       <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
-        <v>43</v>
+      <c r="D15">
+        <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F15" s="4">
         <v>39660</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1589,17 +1580,17 @@
       <c r="C16" t="s">
         <v>38</v>
       </c>
-      <c r="D16" t="s">
-        <v>43</v>
+      <c r="D16">
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="4">
         <v>39463</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1612,17 +1603,17 @@
       <c r="C17" t="s">
         <v>40</v>
       </c>
-      <c r="D17" t="s">
-        <v>43</v>
+      <c r="D17">
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F17" s="4">
         <v>39507</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1635,17 +1626,17 @@
       <c r="C18" t="s">
         <v>39</v>
       </c>
-      <c r="D18" t="s">
-        <v>44</v>
+      <c r="D18">
+        <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F18" s="4">
         <v>39547</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1658,17 +1649,17 @@
       <c r="C19" t="s">
         <v>38</v>
       </c>
-      <c r="D19" t="s">
-        <v>43</v>
+      <c r="D19">
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F19" s="4">
         <v>39644</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1681,17 +1672,17 @@
       <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="D20" t="s">
-        <v>43</v>
+      <c r="D20">
+        <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F20" s="4">
         <v>39992</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1704,11 +1695,11 @@
       <c r="C21" t="s">
         <v>38</v>
       </c>
-      <c r="D21" t="s">
-        <v>44</v>
+      <c r="D21">
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F21" s="4">
         <v>39557</v>
@@ -1727,11 +1718,11 @@
       <c r="C22" t="s">
         <v>38</v>
       </c>
-      <c r="D22" t="s">
-        <v>43</v>
+      <c r="D22">
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F22" s="4">
         <v>39582</v>
@@ -1750,17 +1741,17 @@
       <c r="C23" t="s">
         <v>39</v>
       </c>
-      <c r="D23" t="s">
-        <v>43</v>
+      <c r="D23">
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F23" s="4">
         <v>39682</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1773,17 +1764,17 @@
       <c r="C24" t="s">
         <v>39</v>
       </c>
-      <c r="D24" t="s">
-        <v>44</v>
+      <c r="D24">
+        <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F24" s="4">
         <v>39468</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1796,17 +1787,17 @@
       <c r="C25" t="s">
         <v>40</v>
       </c>
-      <c r="D25" t="s">
-        <v>44</v>
+      <c r="D25">
+        <v>24</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F25" s="4">
         <v>39783</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1819,17 +1810,17 @@
       <c r="C26" t="s">
         <v>38</v>
       </c>
-      <c r="D26" t="s">
-        <v>44</v>
+      <c r="D26">
+        <v>25</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F26" s="4">
         <v>39458</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1842,11 +1833,11 @@
       <c r="C27" t="s">
         <v>38</v>
       </c>
-      <c r="D27" t="s">
-        <v>43</v>
+      <c r="D27">
+        <v>26</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F27" s="4">
         <v>39753</v>
@@ -1865,17 +1856,17 @@
       <c r="C28" t="s">
         <v>40</v>
       </c>
-      <c r="D28" t="s">
-        <v>44</v>
+      <c r="D28">
+        <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F28" s="4">
         <v>39505</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1888,11 +1879,11 @@
       <c r="C29" t="s">
         <v>38</v>
       </c>
-      <c r="D29" t="s">
-        <v>43</v>
+      <c r="D29">
+        <v>28</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F29" s="6">
         <v>39753</v>
@@ -1903,7 +1894,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -1911,11 +1902,11 @@
       <c r="C30" t="s">
         <v>40</v>
       </c>
-      <c r="D30" t="s">
-        <v>43</v>
+      <c r="D30">
+        <v>29</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="9"/>

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC73D70E-9FAD-44D2-BF04-B192888E39D9}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31481BAD-D325-4754-BD91-AAFF5112AAA3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
   <si>
     <t>Jugador</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Jorge_vicaria</t>
   </si>
   <si>
-    <t xml:space="preserve">rodrigo_cueva </t>
-  </si>
-  <si>
     <t xml:space="preserve">Juan_Manuel_Ruiz </t>
   </si>
   <si>
@@ -167,6 +164,75 @@
   </si>
   <si>
     <t>PASSWORD</t>
+  </si>
+  <si>
+    <t>70069983T</t>
+  </si>
+  <si>
+    <t>51742352B</t>
+  </si>
+  <si>
+    <t>49334170K</t>
+  </si>
+  <si>
+    <t>48761553N</t>
+  </si>
+  <si>
+    <t>49592528C</t>
+  </si>
+  <si>
+    <t>51522418A</t>
+  </si>
+  <si>
+    <t>02784916F</t>
+  </si>
+  <si>
+    <t>49410517P</t>
+  </si>
+  <si>
+    <t>52045959H</t>
+  </si>
+  <si>
+    <t>51520055D</t>
+  </si>
+  <si>
+    <t>Z2057025W</t>
+  </si>
+  <si>
+    <t>48149928A</t>
+  </si>
+  <si>
+    <t>51498955T</t>
+  </si>
+  <si>
+    <t>51533428L</t>
+  </si>
+  <si>
+    <t>23933803A</t>
+  </si>
+  <si>
+    <t>54720683A</t>
+  </si>
+  <si>
+    <t>70966992D</t>
+  </si>
+  <si>
+    <t>Z51196298-M</t>
+  </si>
+  <si>
+    <t>49994657V</t>
+  </si>
+  <si>
+    <t>01943462P</t>
+  </si>
+  <si>
+    <t>48159223Y</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_bf7706da387c44bc823e7e5df79bb741~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_902cdb20127140b89dfd6d4fe3f75bf8~mv2.jpeg</t>
   </si>
 </sst>
 </file>
@@ -901,8 +967,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G30" totalsRowShown="0">
-  <autoFilter ref="A1:G30" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G29" totalsRowShown="0">
+  <autoFilter ref="A1:G29" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
@@ -1213,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1233,19 +1299,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s">
         <v>46</v>
-      </c>
-      <c r="G1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1256,19 +1322,17 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="2">
         <v>39786</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1279,19 +1343,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="F3" s="4">
         <v>39461</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1302,19 +1366,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" s="4">
         <v>39544</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1325,19 +1389,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4">
         <v>39672</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1348,19 +1412,19 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="4">
         <v>39519</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1371,19 +1435,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4">
         <v>39512</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1394,19 +1458,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="4">
         <v>39512</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1417,19 +1481,19 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="4">
         <v>39507</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1440,19 +1504,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="4">
         <v>39866</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1463,19 +1527,19 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="4">
         <v>39755</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1486,19 +1550,19 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="4">
         <v>39492</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1509,19 +1573,19 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="4">
         <v>39724</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1532,19 +1596,19 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" s="4">
         <v>39826</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1555,19 +1619,19 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15">
-        <v>14</v>
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" s="4">
         <v>39660</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1578,19 +1642,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="4">
         <v>39463</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1601,19 +1665,19 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17">
-        <v>16</v>
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="4">
         <v>39507</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1624,19 +1688,19 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" s="4">
         <v>39547</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1647,19 +1711,19 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19">
-        <v>18</v>
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>62</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="4">
         <v>39644</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1670,19 +1734,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20">
-        <v>19</v>
+        <v>38</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" s="4">
         <v>39992</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1693,19 +1757,19 @@
         <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="4">
         <v>39557</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1716,19 +1780,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F22" s="4">
         <v>39582</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1739,19 +1803,19 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23">
-        <v>22</v>
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23" s="4">
         <v>39682</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1762,19 +1826,19 @@
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F24" s="4">
         <v>39468</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1785,19 +1849,19 @@
         <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>66</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" s="4">
         <v>39783</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1808,19 +1872,19 @@
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F26" s="4">
         <v>39458</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1831,19 +1895,19 @@
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27">
-        <v>26</v>
+        <v>37</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F27" s="4">
         <v>39753</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1851,71 +1915,51 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28">
+        <v>28</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="6">
+        <v>39753</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
         <v>12</v>
       </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28">
-        <v>27</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="4">
-        <v>39505</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="6">
-        <v>39753</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30">
-        <v>29</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{793807AE-2254-408E-97A4-C80ACB7D2E05}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31481BAD-D325-4754-BD91-AAFF5112AAA3}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43C84C4B-EC4A-4FD0-8644-08FADC7663BB}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
   <si>
     <t>Jugador</t>
   </si>
@@ -151,9 +151,6 @@
     <t>fotos</t>
   </si>
   <si>
-    <t>https://banner2.cleanpng.com/cb2/wms/piv/v21en33wa.webp</t>
-  </si>
-  <si>
     <t>Diestro</t>
   </si>
   <si>
@@ -233,6 +230,75 @@
   </si>
   <si>
     <t>https://static.wixstatic.com/media/8ca434_902cdb20127140b89dfd6d4fe3f75bf8~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_65608b7a07624f28882a31568370548a~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_bc3cf45538bc4e4cb75d023c0c4ed2da~mv2.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_a7d6256cf6b94e6289d8449c07de9b06~mv2.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_3588209afd86455b901323c1cc6b9ae5~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_53cafa564de9472e8b20d0c9b47b3497~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_230a74f2050a445681801cb0bc833646~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_f60030c0a0564e21ac38d0fa76eee0c9~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_9db554cfa678412ebc9b83d11a89acf2~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_e68e49cf1bda45c2b8befefde32069ba~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_8b45f2bb6ee149128f58bfdbf8fe62f3~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_5368fb032d8e4ef08f391e8d5d1d0374~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_bf0a20ee5de6478980610b15cfc0e81d~mv2.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_5e823d9350d4423e8fe7ac5d5fcde058~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_000bef0921e84b3c9710238d2a06cb95~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_7beaa83a151c4f54a39ab07e046361fa~mv2.jpg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_3b5ee5340eae472b99d4e0e9c10ec43b~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_af7ed8b47818491095826c7c8193a02a~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_80e128ee028e4c70af5b7604e9fbf5a4~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_81db1ad8dc014b4cb606ebbda1cd012f~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_7f8e3a5dd8d9462d8f3ee63548c95a38~mv2.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alejandro_Dominguez_Gonzalez </t>
+  </si>
+  <si>
+    <t>02775300M</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_033b3d2a6b0d4dfcbb4e4ef999c63ab7~mv2.png</t>
   </si>
 </sst>
 </file>
@@ -798,7 +864,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="14" fontId="20" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -825,6 +891,10 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -967,8 +1037,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G29" totalsRowShown="0">
-  <autoFilter ref="A1:G29" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G30" totalsRowShown="0">
+  <autoFilter ref="A1:G30" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
@@ -1279,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1302,16 +1372,16 @@
         <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
         <v>42</v>
       </c>
       <c r="F1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" t="s">
         <v>45</v>
-      </c>
-      <c r="G1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1346,16 +1416,16 @@
         <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3" s="4">
         <v>39461</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1369,16 +1439,16 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F4" s="4">
         <v>39544</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1395,13 +1465,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F5" s="4">
         <v>39672</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1415,10 +1485,10 @@
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F6" s="4">
         <v>39519</v>
@@ -1438,16 +1508,16 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F7" s="4">
         <v>39512</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1461,16 +1531,16 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F8" s="4">
         <v>39512</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1484,10 +1554,10 @@
         <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F9" s="4">
         <v>39507</v>
@@ -1507,10 +1577,10 @@
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F10" s="4">
         <v>39866</v>
@@ -1530,16 +1600,16 @@
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F11" s="4">
         <v>39755</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1553,16 +1623,16 @@
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="F12" s="4">
         <v>39492</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1576,10 +1646,10 @@
         <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F13" s="4">
         <v>39724</v>
@@ -1599,16 +1669,14 @@
         <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="4">
         <v>39826</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1622,16 +1690,16 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F15" s="4">
         <v>39660</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1648,13 +1716,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F16" s="4">
         <v>39463</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1668,16 +1736,16 @@
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="F17" s="4">
         <v>39507</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1691,16 +1759,16 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="F18" s="4">
         <v>39547</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1714,16 +1782,16 @@
         <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F19" s="4">
         <v>39644</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1737,16 +1805,16 @@
         <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F20" s="4">
         <v>39992</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1762,9 +1830,7 @@
       <c r="D21">
         <v>20</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="E21" s="1"/>
       <c r="F21" s="4">
         <v>39557</v>
       </c>
@@ -1783,10 +1849,10 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="F22" s="4">
         <v>39582</v>
@@ -1806,16 +1872,16 @@
         <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F23" s="4">
         <v>39682</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1831,14 +1897,12 @@
       <c r="D24">
         <v>23</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="E24" s="1"/>
       <c r="F24" s="4">
         <v>39468</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1852,16 +1916,16 @@
         <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="F25" s="4">
         <v>39783</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1875,16 +1939,16 @@
         <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="F26" s="4">
         <v>39458</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1898,10 +1962,10 @@
         <v>37</v>
       </c>
       <c r="D27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F27" s="4">
         <v>39753</v>
@@ -1923,9 +1987,7 @@
       <c r="D28">
         <v>28</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="6">
         <v>39753</v>
       </c>
@@ -1933,7 +1995,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1947,19 +2009,43 @@
         <v>29</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="12">
+        <v>39517</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{793807AE-2254-408E-97A4-C80ACB7D2E05}"/>
+    <hyperlink ref="E30" r:id="rId2" xr:uid="{2903A663-6F05-4D95-887A-983FD2DF64E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43C84C4B-EC4A-4FD0-8644-08FADC7663BB}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A1E750-ED88-45CE-A7AA-FC0BF1D5DEDA}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
   <sheets>
     <sheet name="Posiciones" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="94">
   <si>
     <t>Jugador</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>https://static.wixstatic.com/media/8ca434_033b3d2a6b0d4dfcbb4e4ef999c63ab7~mv2.png</t>
+  </si>
+  <si>
+    <t>79093971F</t>
   </si>
 </sst>
 </file>
@@ -864,7 +867,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="14" fontId="20" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -891,8 +894,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyBorder="1"/>
   </cellXfs>
@@ -1461,8 +1463,8 @@
       <c r="C5" t="s">
         <v>38</v>
       </c>
-      <c r="D5">
-        <v>4</v>
+      <c r="D5" t="s">
+        <v>93</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>71</v>
@@ -2024,13 +2026,13 @@
       <c r="C30" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="11">
         <v>39517</v>
       </c>
       <c r="G30" s="5" t="s">

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05A1E750-ED88-45CE-A7AA-FC0BF1D5DEDA}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E4CFA7-AB55-44E5-A47D-A02B732177E0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="96">
   <si>
     <t>Jugador</t>
   </si>
@@ -106,9 +106,6 @@
     <t>Alberto_Benedicto_Carpintero</t>
   </si>
   <si>
-    <t>Dennis_Medina</t>
-  </si>
-  <si>
     <t>Ruben_Perez_Curto</t>
   </si>
   <si>
@@ -302,6 +299,15 @@
   </si>
   <si>
     <t>79093971F</t>
+  </si>
+  <si>
+    <t>50365328c</t>
+  </si>
+  <si>
+    <t>51729334B</t>
+  </si>
+  <si>
+    <t>51507405D</t>
   </si>
 </sst>
 </file>
@@ -1039,8 +1045,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G30" totalsRowShown="0">
-  <autoFilter ref="A1:G30" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}" name="Tabla1" displayName="Tabla1" ref="A1:G29" totalsRowShown="0">
+  <autoFilter ref="A1:G29" xr:uid="{97812EF7-7207-445A-B780-D6046FF4E4C8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{9890C0E8-1734-48AB-B9B8-F71F9B0FD391}" name="Jugador"/>
     <tableColumn id="2" xr3:uid="{F74319A2-3299-4382-8CC7-D4EC8D8793AD}" name="Posicion"/>
@@ -1351,7 +1357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86862050-FDEA-4FB1-B5DB-6F278968DFB2}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -1371,19 +1377,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
         <v>44</v>
-      </c>
-      <c r="G1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1394,17 +1400,17 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>95</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2">
         <v>39786</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1415,19 +1421,19 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" s="4">
         <v>39461</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1438,19 +1444,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" s="4">
         <v>39544</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1461,19 +1467,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" s="4">
         <v>39672</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1484,19 +1490,19 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" s="4">
         <v>39519</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1507,19 +1513,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="4">
         <v>39512</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1530,19 +1536,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="4">
         <v>39512</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1553,19 +1559,19 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="4">
         <v>39507</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1576,19 +1582,19 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="4">
         <v>39866</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1599,19 +1605,19 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" s="4">
         <v>39755</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1622,19 +1628,19 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" s="4">
         <v>39492</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1645,19 +1651,19 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" s="4">
         <v>39724</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1668,17 +1674,17 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="4">
         <v>39826</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1689,19 +1695,19 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F15" s="4">
         <v>39660</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1712,19 +1718,19 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F16" s="4">
         <v>39463</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1735,19 +1741,19 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" s="4">
         <v>39507</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1758,19 +1764,19 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18" s="4">
         <v>39547</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1781,19 +1787,17 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E19" s="1"/>
       <c r="F19" s="4">
         <v>39644</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1804,19 +1808,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F20" s="4">
         <v>39992</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1824,20 +1828,22 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="F21" s="4">
-        <v>39557</v>
+        <v>39582</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1845,7 +1851,7 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
@@ -1857,10 +1863,10 @@
         <v>85</v>
       </c>
       <c r="F22" s="4">
-        <v>39582</v>
+        <v>39682</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1871,19 +1877,17 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>86</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="E23" s="1"/>
       <c r="F23" s="4">
-        <v>39682</v>
+        <v>39468</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1891,20 +1895,22 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
       </c>
-      <c r="D24">
-        <v>23</v>
-      </c>
-      <c r="E24" s="1"/>
+      <c r="D24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="F24" s="4">
-        <v>39468</v>
+        <v>39783</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1912,10 +1918,10 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -1924,10 +1930,10 @@
         <v>87</v>
       </c>
       <c r="F25" s="4">
-        <v>39783</v>
+        <v>39458</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1935,22 +1941,22 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="F26" s="4">
-        <v>39458</v>
+        <v>39753</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1958,92 +1964,69 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="4">
+        <v>36</v>
+      </c>
+      <c r="D27">
+        <v>28</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="6">
         <v>39753</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>40</v>
+      <c r="G27" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
         <v>3</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>37</v>
       </c>
-      <c r="D28">
-        <v>28</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="6">
-        <v>39753</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29">
-        <v>29</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
+      <c r="D29" t="s">
         <v>90</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E29" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="11">
+      <c r="F29" s="11">
         <v>39517</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>43</v>
+      <c r="G29" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{793807AE-2254-408E-97A4-C80ACB7D2E05}"/>
-    <hyperlink ref="E30" r:id="rId2" xr:uid="{2903A663-6F05-4D95-887A-983FD2DF64E6}"/>
+    <hyperlink ref="E29" r:id="rId2" xr:uid="{2903A663-6F05-4D95-887A-983FD2DF64E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4E4CFA7-AB55-44E5-A47D-A02B732177E0}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C0C54E-B0F5-45AE-82FB-3651010EF084}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="99">
   <si>
     <t>Jugador</t>
   </si>
@@ -308,6 +308,15 @@
   </si>
   <si>
     <t>51507405D</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_bcdf89ecefb2483687662aec37f0cdec~mv2.jpeg</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_8be82db4306b44649ee912ca9d5c7db4~mv2.png</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_900f2573b3aa4853954ab0005ec5aa88~mv2.png</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1414,9 @@
       <c r="D2" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="F2" s="2">
         <v>39786</v>
       </c>
@@ -1792,7 +1803,9 @@
       <c r="D19" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="F19" s="4">
         <v>39644</v>
       </c>
@@ -1882,7 +1895,9 @@
       <c r="D23" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="F23" s="4">
         <v>39468</v>
       </c>
@@ -2027,10 +2042,11 @@
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{793807AE-2254-408E-97A4-C80ACB7D2E05}"/>
     <hyperlink ref="E29" r:id="rId2" xr:uid="{2903A663-6F05-4D95-887A-983FD2DF64E6}"/>
+    <hyperlink ref="E19" r:id="rId3" xr:uid="{4376FC9B-16F2-4F4B-89D6-FE200E74D3BC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5C0C54E-B0F5-45AE-82FB-3651010EF084}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2466ED8C-6C68-40D6-83AF-66F5C70DF5ED}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="100">
   <si>
     <t>Jugador</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>https://static.wixstatic.com/media/8ca434_900f2573b3aa4853954ab0005ec5aa88~mv2.png</t>
+  </si>
+  <si>
+    <t>05994240A</t>
   </si>
 </sst>
 </file>
@@ -1731,8 +1734,8 @@
       <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="D16">
-        <v>15</v>
+      <c r="D16" t="s">
+        <v>99</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>80</v>

--- a/data/Posiciones.xlsx
+++ b/data/Posiciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2466ED8C-6C68-40D6-83AF-66F5C70DF5ED}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{ACE6BB03-6350-4C05-B9B8-BD6413AAC410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6536530B-2EA3-42E4-9D38-2F86C06230EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B961EC1D-9D64-4A12-AB9D-930ACB18AE51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="102">
   <si>
     <t>Jugador</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>05994240A</t>
+  </si>
+  <si>
+    <t>05725364C</t>
+  </si>
+  <si>
+    <t>https://static.wixstatic.com/media/8ca434_1b15a2b8907a420db35f4fd7a8a4ac97~mv2.png</t>
   </si>
 </sst>
 </file>
@@ -1987,10 +1993,12 @@
       <c r="C27" t="s">
         <v>36</v>
       </c>
-      <c r="D27">
-        <v>28</v>
-      </c>
-      <c r="E27" s="1"/>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="F27" s="6">
         <v>39753</v>
       </c>
